--- a/docs/demo-materials/contract-sample-tests/合同样例-测试导入样本-空值与非法编码.xlsx
+++ b/docs/demo-materials/contract-sample-tests/合同样例-测试导入样本-空值与非法编码.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入样本" sheetId="1" r:id="Rd69da9a9d6e14692"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入样本" sheetId="1" r:id="R177e3db120f64500"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -334,7 +334,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab1a6ffce70b44a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd92a38d4f83d4161"/>
   </x:tableParts>
 </x:worksheet>
 </file>